--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
@@ -3628,7 +3628,7 @@
     <row r="14" ht="36" customHeight="1" s="72">
       <c r="B14" s="89" t="inlineStr">
         <is>
-          <t>최종 견적 금액 : 일금 일억구천삼백사십팔만일천팔백팔원 정(193,481,808원) (VAT 별도)</t>
+          <t>최종 견적 금액 : 일금 이억이천만원 정(220,000,000원) (VAT 별도)</t>
         </is>
       </c>
       <c r="C14" s="90" t="n"/>
@@ -3921,7 +3921,7 @@
       <c r="D23" s="125" t="n"/>
       <c r="E23" s="126" t="inlineStr">
         <is>
-          <t>- 제공 기술에 대한 일반 재경비</t>
+          <t>- 재경비 (일반관리비, 직접인건비의 6%)</t>
         </is>
       </c>
       <c r="F23" s="124" t="inlineStr">
@@ -3940,11 +3940,15 @@
         </is>
       </c>
       <c r="I23" s="127">
-        <f>I22*0%</f>
+        <f>ROUND(I22*6%,0)</f>
         <v/>
       </c>
       <c r="J23" s="127" t="n"/>
-      <c r="K23" s="128" t="n"/>
+      <c r="K23" s="128" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="39.95" customHeight="1" s="72">
       <c r="B24" s="102" t="n">
@@ -3958,7 +3962,7 @@
       <c r="D24" s="125" t="n"/>
       <c r="E24" s="126" t="inlineStr">
         <is>
-          <t>- 제공 기술료</t>
+          <t>- 기술료 (이윤 상당, 10% 이내)</t>
         </is>
       </c>
       <c r="F24" s="103" t="inlineStr">
@@ -3976,12 +3980,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="107">
-        <f>(I22+I23)*0</f>
-        <v/>
+      <c r="I24" s="107" t="n">
+        <v>14909284</v>
       </c>
       <c r="J24" s="107" t="n"/>
-      <c r="K24" s="129" t="n"/>
+      <c r="K24" s="129" t="inlineStr">
+        <is>
+          <t>7.27%</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="39.95" customHeight="1" s="72">
       <c r="B25" s="130" t="inlineStr">
@@ -4011,9 +4018,8 @@
         <f>SUM(I23:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="121">
-        <f>I25</f>
-        <v/>
+      <c r="J25" s="121" t="n">
+        <v>0</v>
       </c>
       <c r="K25" s="122" t="n"/>
     </row>
@@ -4092,14 +4098,14 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="52" customHeight="1" s="72">
+    <row r="29" ht="62" customHeight="1" s="72">
       <c r="B29" s="145" t="inlineStr">
         <is>
           <t>※ 비 고
    - 본 견적은 전자통관국제협력재단 'CUPIA AI 연구 과제 2026' 중 과제 2(EWACS 복합 AI Agent 구축, 총 22 M/M)에 한한 견적임 (과제 1 e-PASS AI 모델 상품화는 수행 완료로 제외)
-   - 인원·투입월(M/M)은 과업지시서(CUPIA-AI-2026-SOW-001) 6.2 투입 인력 기준이며, 투입 시기는 계약 착수 시점에 따라 조정함
-   - 단가는 SW기술자 직무별 평균임금 체계를 따른 당사 표준 단가 기준이며, 최종 단가는 예정가격 협의 시 조정 가능함
-   - 상기 금액은 부가가치세(VAT) 별도이며, 재경비·기술료 및 계약보증금·검수·지급 방식 등 계약 조건은 계약서에 따름</t>
+   - 인원·투입월(M/M)은 과업지시서(CUPIA-AI-2026-SOW-001) 6.2 투입 인력 기준이며, 단가는 SW기술자 직무별 평균임금 체계를 따른 당사 표준 단가 기준임
+   - 재경비·기술료는 원가계산 기준(국가계약법 시행규칙 제8조 예정가격 작성기준의 일반관리비 6%·이윤 10% 상한, 재단 계약관리 시행세칙 제24조)에 따라 산정함
+   - 상기 금액은 부가가치세(VAT) 별도이며, 최종 금액·계약 조건은 예정가격 협의 및 계약서에 따름</t>
         </is>
       </c>
       <c r="C29" s="137" t="n"/>
@@ -4112,7 +4118,7 @@
       <c r="J29" s="137" t="n"/>
       <c r="K29" s="146" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1" s="72">
+    <row r="30" ht="62" customHeight="1" s="72">
       <c r="B30" s="141" t="n"/>
       <c r="C30" s="142" t="n"/>
       <c r="D30" s="142" t="n"/>

--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'견적서(인력)'!$A$1:$L$34</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I17" s="107">
         <f>F17*G17*H17</f>
-        <v/>
+        <v>74543819</v>
       </c>
       <c r="J17" s="108" t="n">
         <v>0</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="I18" s="107">
         <f>F18*G18*H18</f>
-        <v/>
+        <v>46524744</v>
       </c>
       <c r="J18" s="108" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="I19" s="107">
         <f>F19*G19*H19</f>
-        <v/>
+        <v>27606640</v>
       </c>
       <c r="J19" s="108" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I20" s="107">
         <f>F20*G20*H20</f>
-        <v/>
+        <v>33126213</v>
       </c>
       <c r="J20" s="108" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="I21" s="107">
         <f>F21*G21*H21</f>
-        <v/>
+        <v>11680392</v>
       </c>
       <c r="J21" s="108" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I22" s="120">
         <f>SUM(I17:I21)</f>
-        <v/>
+        <v>193481808</v>
       </c>
       <c r="J22" s="121" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I23" s="127">
         <f>ROUND(I22*6%,0)</f>
-        <v/>
+        <v>11608908</v>
       </c>
       <c r="J23" s="127" t="n"/>
       <c r="K23" s="128" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="I25" s="120">
         <f>SUM(I23:I24)</f>
-        <v/>
+        <v>26518192</v>
       </c>
       <c r="J25" s="121" t="n">
         <v>0</v>
@@ -4049,11 +4049,11 @@
       </c>
       <c r="I26" s="134">
         <f>I22+I25</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="J26" s="134">
         <f>J22+J25</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K26" s="135" t="n"/>
     </row>
@@ -4071,11 +4071,11 @@
       <c r="H27" s="93" t="n"/>
       <c r="I27" s="138">
         <f>I26</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="J27" s="139">
         <f>I26</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="K27" s="140" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       <c r="J28" s="143" t="n"/>
       <c r="K28" s="144">
         <f>100%-(J27/I27)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="62" customHeight="1" s="72">

--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_1.xlsx
@@ -4102,10 +4102,10 @@
       <c r="B29" s="145" t="inlineStr">
         <is>
           <t>※ 비 고
-   - 본 견적은 전자통관국제협력재단 'CUPIA AI 연구 과제 2026' 중 과제 2(EWACS 복합 AI Agent 구축, 총 22 M/M)에 한한 견적임 (과제 1 e-PASS AI 모델 상품화는 수행 완료로 제외)
+   - 본 견적은 전자통관국제협력재단 'CUPIA AI 연구 과제 2026' 과제 2(EWACS 복합 AI Agent 구축, 총 22 M/M)에 대한 견적임
    - 인원·투입월(M/M)은 과업지시서(CUPIA-AI-2026-SOW-001) 6.2 투입 인력 기준이며, 단가는 SW기술자 직무별 평균임금 체계를 따른 당사 표준 단가 기준임
-   - 재경비·기술료는 원가계산 기준(국가계약법 시행규칙 제8조 예정가격 작성기준의 일반관리비 6%·이윤 10% 상한, 재단 계약관리 시행세칙 제24조)에 따라 산정함
-   - 상기 금액은 부가가치세(VAT) 별도이며, 최종 금액·계약 조건은 예정가격 협의 및 계약서에 따름</t>
+   - 재경비(일반관리비 6%)·기술료(이윤 10% 이내)는 국가계약법 시행규칙 제8조 및 재단 계약관리 시행세칙 제24조의 원가계산 기준에 따라 산정함
+   - 상기 금액은 부가가치세(VAT) 별도이며, 계약 조건은 계약서에 따름</t>
         </is>
       </c>
       <c r="C29" s="137" t="n"/>
